--- a/frontend/src/assets/files/notice-data.xlsx
+++ b/frontend/src/assets/files/notice-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B289BFAF-2ABE-457C-B0AA-3B78F0868DFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5C285B-E3F0-47D7-9270-B0797C0F74A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="100">
   <si>
     <t>카테고리</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>안내</t>
-  </si>
-  <si>
-    <t>[안내] 시스템 이용약관 개정</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -62,9 +59,6 @@
     <t>이중앙</t>
   </si>
   <si>
-    <t>[안내] 개인정보 처리방침 변경</t>
-  </si>
-  <si>
     <t>안녕하세요. 시설팀 입니다.
 개인정보 처리방침이 변경되었습니다. 주요 변경 내용을 확인하시고 서비스를 이용해 주시기 바랍니다.
 1. 변경 항목
@@ -72,9 +66,6 @@
 - 제3자 제공 조건 명확화
 2. 시행일: 2026년 3월 1일
 문의: 시설팀 (내선번호 : 9000)</t>
-  </si>
-  <si>
-    <t>[안내] 빠른 고장 신고 가이드</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -152,9 +143,6 @@
   </si>
   <si>
     <t>2026.02.18</t>
-  </si>
-  <si>
-    <t>신규 서비스</t>
   </si>
   <si>
     <t>모바일 고장 신고 앱 출시 안내</t>
@@ -193,7 +181,23 @@
     <t>시설 관리 시스템 v2.0 업데이트</t>
   </si>
   <si>
-    <t>안녕하세요. 시설팀 입니다.
+    <t>2026.02.05</t>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시스템 이용약관 개정</t>
+  </si>
+  <si>
+    <t>개인정보 처리방침 변경</t>
+  </si>
+  <si>
+    <t>빠른 고장 신고 가이드</t>
+  </si>
+  <si>
+    <t>안녕하세요. 전산정보팀 입니다.
 시설 관리 시스템이 v2.0으로 업데이트 되었습니다.
 주요 변경 사항:
 - UI/UX 전면 개편
@@ -204,11 +208,336 @@
 문의: 시설팀 (내선번호 : 9000)</t>
   </si>
   <si>
-    <t>2026.02.05</t>
-  </si>
-  <si>
-    <t>NO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>공지</t>
+  </si>
+  <si>
+    <t>2026년 상반기 시설 점검 일정 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+2026년 상반기 정기 시설 점검 일정을 공지드립니다.
+1. 소방 설비 점검: 2026년 4월 10일
+2. 전기 설비 점검: 2026년 4월 24일
+3. 가스 설비 점검: 2026년 5월 8일
+점검 당일 해당 구역 출입이 제한될 수 있으니 협조 부탁드립니다.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.28</t>
+  </si>
+  <si>
+    <t>긴급</t>
+  </si>
+  <si>
+    <t>A동 3층 누수 긴급 점검 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+A동 3층 일부 구역에서 누수가 발생하여 긴급 점검이 진행됩니다.
+- 점검 시간: 즉시 ~ 복구 완료 시까지
+- 점검 구역: A동 3층 301~310호
+- 수도 일시 중단 예정
+입주민 여러분의 양해를 부탁드립니다.
+긴급 문의: 010-9999-0000</t>
+  </si>
+  <si>
+    <t>2026.03.25</t>
+  </si>
+  <si>
+    <t>안전</t>
+  </si>
+  <si>
+    <t>화재 대피 훈련 실시 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 안전관리팀 입니다.
+화재 대피 훈련을 실시합니다.
+- 일시: 2026년 4월 5일 (일) 오전 10시
+- 대상: 전 입주민
+- 내용: 비상구 확인 및 대피 요령 숙지
+훈련 중 비상벨이 울리더라도 당황하지 마시고 안내에 따라 주세요.
+문의: 안전관리팀 (내선번호 : 9100)</t>
+  </si>
+  <si>
+    <t>2026.03.22</t>
+  </si>
+  <si>
+    <t>모바일 앱 v1.5 업데이트 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 전산정보팀 입니다.
+모바일 앱이 v1.5로 업데이트되었습니다.
+주요 변경 사항:
+- 버그 수정 (로그인 오류 개선)
+- 신고 내역 필터 기능 추가
+- 다크 모드 지원
+- 성능 최적화
+앱스토어에서 최신 버전으로 업데이트해 주세요.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.20</t>
+  </si>
+  <si>
+    <t>지하 주차장 CCTV 점검 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+지하 주차장 CCTV 정기 점검이 실시됩니다.
+- 점검 일시: 2026년 3월 30일 (월) 오후 2시 ~ 5시
+- 점검 구역: 지하 1층~지하 3층 전 구역
+- 점검 내용: 카메라 렌즈 청소, 녹화 상태 확인
+점검 시간 동안 CCTV 일부가 일시 중단될 수 있습니다.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.18</t>
+  </si>
+  <si>
+    <t>봄철 조경 작업 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+봄철 단지 내 조경 정비 작업이 진행됩니다.
+- 작업 기간: 2026년 3월 25일 ~ 4월 5일
+- 작업 내용: 잔디 보식, 화단 정비, 수목 전지
+- 작업 시간: 오전 9시 ~ 오후 6시
+작업 기간 중 소음이 발생할 수 있으니 양해 부탁드립니다.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.15</t>
+  </si>
+  <si>
+    <t>입주민 커뮤니티 센터 운영 시간 변경</t>
+  </si>
+  <si>
+    <t>안녕하세요. 관리사무소 입니다.
+커뮤니티 센터 운영 시간이 변경됩니다.
+변경 전:
+- 평일 09:00 ~ 21:00
+- 주말 10:00 ~ 20:00
+변경 후 (4월 1일부터):
+- 평일 07:00 ~ 22:00
+- 주말 08:00 ~ 21:00
+더 많은 분들이 이용하실 수 있도록 운영 시간을 확대하였습니다.
+문의: 관리사무소 (내선번호 : 9010)</t>
+  </si>
+  <si>
+    <t>2026.03.12</t>
+  </si>
+  <si>
+    <t>어린이 놀이터 안전 점검 결과 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 안전관리팀 입니다.
+어린이 놀이터 정기 안전 점검 결과를 안내드립니다.
+점검 결과:
+- 미끄럼틀: 양호
+- 그네: 체인 교체 완료
+- 모래밭: 이물질 제거 완료
+- 안전 매트: 일부 교체 진행 중 (3월 20일 완료 예정)
+안전한 놀이 환경을 위해 최선을 다하겠습니다.
+문의: 안전관리팀 (내선번호 : 9100)</t>
+  </si>
+  <si>
+    <t>2026.03.10</t>
+  </si>
+  <si>
+    <t>정전 발생 안내 및 복구 완료</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+금일 오전 B동 일부 구역에서 정전이 발생하였으나 복구 완료되었습니다.
+- 정전 발생: 03월 08일 오전 11:20
+- 복구 완료: 03월 08일 오후 12:45
+- 영향 구역: B동 5층 ~ 8층
+불편을 드려 죄송합니다. 원인 분석 후 재발 방지 조치를 취하겠습니다.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.08</t>
+  </si>
+  <si>
+    <t>통합 관리 시스템 보안 패치 적용</t>
+  </si>
+  <si>
+    <t>안녕하세요. 전산정보팀 입니다.
+시스템 보안 강화를 위한 패치가 적용됩니다.
+- 작업 일시: 2026년 3월 15일 (일) 새벽 02:00 ~ 04:00
+- 작업 내용: 보안 취약점 패치, SSL 인증서 갱신
+- 서비스 중단: 작업 시간 동안 앱 접속 불가
+보안 강화를 위한 점검이니 양해 부탁드립니다.
+문의: 전산정보팀 (내선번호 : 9200)</t>
+  </si>
+  <si>
+    <t>2026.03.05</t>
+  </si>
+  <si>
+    <t>분리수거 요일 변경 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 관리사무소 입니다.
+분리수거 수거 요일이 변경됩니다.
+변경 전:
+- 종이류: 매주 화요일
+- 캔/병류: 매주 목요일
+변경 후 (3월 16일부터):
+- 종이류: 매주 월요일, 목요일
+- 캔/병류: 매주 화요일, 금요일
+올바른 분리수거로 깨끗한 환경 만들기에 협조해 주세요.
+문의: 관리사무소 (내선번호 : 9010)</t>
+  </si>
+  <si>
+    <t>2026.03.03</t>
+  </si>
+  <si>
+    <t>옥상 방수 공사 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+건물 옥상 방수 공사가 진행됩니다.
+- 공사 기간: 2026년 3월 10일 ~ 3월 20일
+- 공사 건물: A동, C동 옥상
+- 공사 시간: 오전 8시 ~ 오후 6시
+- 옥상 출입 통제: 공사 기간 중 전면 금지
+낙하물 위험이 있으니 공사 구역 접근에 주의해 주세요.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.03.01</t>
+  </si>
+  <si>
+    <t>2026년 관리비 납부 일정 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 관리사무소 입니다.
+2026년 관리비 납부 일정을 안내드립니다.
+납부 기간: 매월 1일 ~ 25일
+납부 방법:
+1. 자동이체 (권장)
+2. 관리사무소 직접 납부
+3. 계좌이체 (예금주: ○○관리단)
+연체 시 연체료가 부과되오니 기간 내 납부 부탁드립니다.
+문의: 관리사무소 (내선번호 : 9010)</t>
+  </si>
+  <si>
+    <t>2026.02.28</t>
+  </si>
+  <si>
+    <t>미세먼지 대응 실내 환기 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 안전관리팀 입니다.
+봄철 미세먼지 농도 상승에 따른 실내 환기 안내드립니다.
+권장 사항:
+- 미세먼지 '나쁨' 이상 시 창문 닫기
+- 공기청정기 가동 권장
+- 외출 시 마스크 착용
+- 귀가 후 손발 세척
+미세먼지 정보는 '에어코리아' 앱에서 실시간 확인 가능합니다.
+문의: 안전관리팀 (내선번호 : 9100)</t>
+  </si>
+  <si>
+    <t>2026.02.26</t>
+  </si>
+  <si>
+    <t>주차 관제 시스템 업그레이드 완료</t>
+  </si>
+  <si>
+    <t>안녕하세요. 전산정보팀 입니다.
+주차 관제 시스템 업그레이드가 완료되었습니다.
+개선 사항:
+- 차량 번호 인식률 향상 (98% → 99.5%)
+- 입출차 처리 속도 개선
+- 실시간 주차 현황 앱 연동
+- 방문 차량 사전 등록 기능 추가
+앱에서 실시간 주차 현황을 확인하실 수 있습니다.
+문의: 전산정보팀 (내선번호 : 9200)</t>
+  </si>
+  <si>
+    <t>2026.02.25</t>
+  </si>
+  <si>
+    <t>수도 단수 긴급 공지</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+배관 수리로 인한 단수가 진행됩니다.
+- 단수 일시: 2026년 2월 24일 (화) 오전 9시 ~ 오후 1시
+- 단수 구역: 전 동 (A, B, C동)
+- 원인: 주배관 노후화로 인한 긴급 교체
+단수 전 필요한 물을 미리 받아 놓으시기 바랍니다.
+복구 완료 후 개별 안내 예정입니다.
+긴급 문의: 010-9999-0000</t>
+  </si>
+  <si>
+    <t>2026.02.23</t>
+  </si>
+  <si>
+    <t>택배 보관함 이용 방법 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 관리사무소 입니다.
+무인 택배 보관함 이용 방법을 안내드립니다.
+1. 보관함 위치: 각 동 1층 로비
+2. 보관 기간: 최대 3일 (초과 시 관리사무소 보관)
+3. 수령 방법: 배송 완료 문자의 인증번호 입력
+4. 대형 택배: 관리사무소에서 별도 수령
+보관 기간 초과 시 반송될 수 있으니 주의 바랍니다.
+문의: 관리사무소 (내선번호 : 9010)</t>
+  </si>
+  <si>
+    <t>2026.02.22</t>
+  </si>
+  <si>
+    <t>보일러 배관 동파 점검 완료 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 시설팀 입니다.
+한파 대비 보일러 배관 동파 여부 점검이 완료되었습니다.
+점검 결과:
+- A동: 이상 없음
+- B동: 203호 배관 보온재 교체 완료
+- C동: 이상 없음
+개별 세대에서도 수시로 확인해 주시기 바라며, 이상 발견 시 즉시 신고해 주세요.
+문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>입주민 대표 회의 결과 공지</t>
+  </si>
+  <si>
+    <t>안녕하세요. 관리사무소 입니다.
+2026년 2월 정기 입주민 대표 회의 결과를 공지드립니다.
+주요 결정 사항:
+1. 공용 전기료 절감을 위한 LED 교체 추진
+2. 단지 내 CCTV 추가 설치 (15대)
+3. 방문 차량 주차 시간 확대 (2시간 → 4시간)
+4. 어린이 놀이터 시설 교체 예산 승인
+다음 회의: 2026년 3월 정기 회의 예정
+문의: 관리사무소 (내선번호 : 9010)</t>
+  </si>
+  <si>
+    <t>2026.02.14</t>
+  </si>
+  <si>
+    <t>겨울철 빙판길 안전 사고 예방 안내</t>
+  </si>
+  <si>
+    <t>안녕하세요. 안전관리팀 입니다.
+겨울철 단지 내 빙판길 안전 사고 예방을 위해 안내드립니다.
+관리 현황:
+- 주요 보행로 염화칼슘 살포 완료
+- 지하 주차장 입구 미끄럼 방지 매트 설치
+- 경사로 구간 모래 포대 비치
+주의 사항:
+- 보행 시 핸드폰 사용 자제
+- 급격한 방향 전환 금지
+- 운동화보다 미끄럼 방지 신발 착용 권장
+문의: 안전관리팀 (내선번호 : 9100)</t>
+  </si>
+  <si>
+    <t>2026.02.08</t>
   </si>
 </sst>
 </file>
@@ -226,6 +555,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -248,7 +578,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -271,20 +601,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -600,223 +945,623 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="C17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>24</v>
+      <c r="B31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/notice-data.xlsx
+++ b/frontend/src/assets/files/notice-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5C285B-E3F0-47D7-9270-B0797C0F74A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0F2EFA-8330-4D64-9387-62F28DE2703B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,10 +184,6 @@
     <t>2026.02.05</t>
   </si>
   <si>
-    <t>NO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시스템 이용약관 개정</t>
   </si>
   <si>
@@ -538,6 +534,10 @@
   </si>
   <si>
     <t>2026.02.08</t>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
@@ -992,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>9</v>
@@ -1012,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -1169,16 +1169,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>8</v>
@@ -1189,16 +1189,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>17</v>
@@ -1209,16 +1209,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -1232,13 +1232,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>21</v>
@@ -1252,13 +1252,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>17</v>
@@ -1272,13 +1272,13 @@
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -1289,16 +1289,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -1309,16 +1309,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -1329,16 +1329,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>17</v>
@@ -1352,13 +1352,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>21</v>
@@ -1372,13 +1372,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>8</v>
@@ -1392,13 +1392,13 @@
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>17</v>
@@ -1409,16 +1409,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
@@ -1429,16 +1429,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>13</v>
@@ -1452,13 +1452,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>21</v>
@@ -1469,16 +1469,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>17</v>
@@ -1492,13 +1492,13 @@
         <v>5</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>8</v>
@@ -1512,10 +1512,10 @@
         <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>24</v>
@@ -1529,16 +1529,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>13</v>
@@ -1549,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>

--- a/frontend/src/assets/files/notice-data.xlsx
+++ b/frontend/src/assets/files/notice-data.xlsx
@@ -1,43 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0F2EFA-8330-4D64-9387-62F28DE2703B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3A0F2EFA-8330-4D64-9387-62F28DE2703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A307FC45-F12A-4303-8964-E1303CBCD671}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공지사항" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="100">
   <si>
-    <t>카테고리</t>
-  </si>
-  <si>
-    <t>제목</t>
-  </si>
-  <si>
-    <t>내용</t>
-  </si>
-  <si>
-    <t>작성일자</t>
-  </si>
-  <si>
-    <t>작성자</t>
+    <t>notice_id</t>
+  </si>
+  <si>
+    <t>notice_category</t>
+  </si>
+  <si>
+    <t>notice_title</t>
+  </si>
+  <si>
+    <t>notice_content</t>
+  </si>
+  <si>
+    <t>notice_at</t>
+  </si>
+  <si>
+    <t>notice_by</t>
   </si>
   <si>
     <t>안내</t>
+  </si>
+  <si>
+    <t>시스템 이용약관 개정</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -59,6 +81,9 @@
     <t>이중앙</t>
   </si>
   <si>
+    <t>개인정보 처리방침 변경</t>
+  </si>
+  <si>
     <t>안녕하세요. 시설팀 입니다.
 개인정보 처리방침이 변경되었습니다. 주요 변경 내용을 확인하시고 서비스를 이용해 주시기 바랍니다.
 1. 변경 항목
@@ -66,6 +91,9 @@
 - 제3자 제공 조건 명확화
 2. 시행일: 2026년 3월 1일
 문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>빠른 고장 신고 가이드</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -179,18 +207,6 @@
   </si>
   <si>
     <t>시설 관리 시스템 v2.0 업데이트</t>
-  </si>
-  <si>
-    <t>2026.02.05</t>
-  </si>
-  <si>
-    <t>시스템 이용약관 개정</t>
-  </si>
-  <si>
-    <t>개인정보 처리방침 변경</t>
-  </si>
-  <si>
-    <t>빠른 고장 신고 가이드</t>
   </si>
   <si>
     <t>안녕하세요. 전산정보팀 입니다.
@@ -202,6 +218,9 @@
 - 다국어 지원 (한국어, 영어)
 업데이트 관련 문의사항은 아래로 연락 주세요.
 문의: 시설팀 (내선번호 : 9000)</t>
+  </si>
+  <si>
+    <t>2026.02.05</t>
   </si>
   <si>
     <t>공지</t>
@@ -535,16 +554,12 @@
   <si>
     <t>2026.02.08</t>
   </si>
-  <si>
-    <t>번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,7 +637,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -633,7 +648,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -934,7 +949,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -944,624 +959,624 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="140.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="140.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="140.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="165.75">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="140.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="140.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="191.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="165.75">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="140.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="140.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="191.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="153">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="165.75">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="165.75">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="165.75">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="153">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="153">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="153">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="165.75">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="191.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/notice-data.xlsx
+++ b/frontend/src/assets/files/notice-data.xlsx
@@ -1,65 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3A0F2EFA-8330-4D64-9387-62F28DE2703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A307FC45-F12A-4303-8964-E1303CBCD671}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981C5FCB-9C3C-4305-B896-0E737D9424D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공지사항" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="100">
   <si>
-    <t>notice_id</t>
-  </si>
-  <si>
-    <t>notice_category</t>
-  </si>
-  <si>
-    <t>notice_title</t>
-  </si>
-  <si>
-    <t>notice_content</t>
-  </si>
-  <si>
-    <t>notice_at</t>
-  </si>
-  <si>
-    <t>notice_by</t>
-  </si>
-  <si>
     <t>안내</t>
-  </si>
-  <si>
-    <t>시스템 이용약관 개정</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -81,9 +44,6 @@
     <t>이중앙</t>
   </si>
   <si>
-    <t>개인정보 처리방침 변경</t>
-  </si>
-  <si>
     <t>안녕하세요. 시설팀 입니다.
 개인정보 처리방침이 변경되었습니다. 주요 변경 내용을 확인하시고 서비스를 이용해 주시기 바랍니다.
 1. 변경 항목
@@ -91,9 +51,6 @@
 - 제3자 제공 조건 명확화
 2. 시행일: 2026년 3월 1일
 문의: 시설팀 (내선번호 : 9000)</t>
-  </si>
-  <si>
-    <t>빠른 고장 신고 가이드</t>
   </si>
   <si>
     <t>안녕하세요. 시설팀 입니다.
@@ -207,6 +164,18 @@
   </si>
   <si>
     <t>시설 관리 시스템 v2.0 업데이트</t>
+  </si>
+  <si>
+    <t>2026.02.05</t>
+  </si>
+  <si>
+    <t>시스템 이용약관 개정</t>
+  </si>
+  <si>
+    <t>개인정보 처리방침 변경</t>
+  </si>
+  <si>
+    <t>빠른 고장 신고 가이드</t>
   </si>
   <si>
     <t>안녕하세요. 전산정보팀 입니다.
@@ -218,9 +187,6 @@
 - 다국어 지원 (한국어, 영어)
 업데이트 관련 문의사항은 아래로 연락 주세요.
 문의: 시설팀 (내선번호 : 9000)</t>
-  </si>
-  <si>
-    <t>2026.02.05</t>
   </si>
   <si>
     <t>공지</t>
@@ -554,12 +520,36 @@
   <si>
     <t>2026.02.08</t>
   </si>
+  <si>
+    <t>notice_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>notice_category</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>notice_title</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>notice_content</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>noticed_at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>noticed_by</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,6 +573,11 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -635,9 +630,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -646,9 +641,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -949,7 +947,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -959,628 +957,629 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="140.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="140.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="140.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="165.75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="140.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="140.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="191.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="165.75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="140.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="140.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="191.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="153">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="153" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="165.75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="165.75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="165.75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="153">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="153" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="153">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="153" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="153">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="153" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="165.75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="191.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/frontend/src/assets/files/notice-data.xlsx
+++ b/frontend/src/assets/files/notice-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981C5FCB-9C3C-4305-B896-0E737D9424D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6202AFB-1DA7-4D28-992C-945CF60DFAAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="98">
   <si>
     <t>안내</t>
   </si>
@@ -41,9 +41,6 @@
     <t>2026.02.20</t>
   </si>
   <si>
-    <t>이중앙</t>
-  </si>
-  <si>
     <t>안녕하세요. 시설팀 입니다.
 개인정보 처리방침이 변경되었습니다. 주요 변경 내용을 확인하시고 서비스를 이용해 주시기 바랍니다.
 1. 변경 항목
@@ -74,9 +71,6 @@
 문의: 시설팀 (내선번호 : 9000)</t>
   </si>
   <si>
-    <t>김관리</t>
-  </si>
-  <si>
     <t>점검</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
 문의: 시설팀 (내선번호 : 9000)</t>
   </si>
   <si>
-    <t>박점검</t>
-  </si>
-  <si>
     <t>업데이트</t>
   </si>
   <si>
@@ -110,9 +101,6 @@
 - 응답 속도 개선 (약 30% 향상)
 앱 사용 중 불편하신 점이 있으시면 신고해 주시기 바랍니다.
 문의: 시설팀 (내선번호 : 9000)</t>
-  </si>
-  <si>
-    <t>최개발</t>
   </si>
   <si>
     <t>엘리베이터 정기 점검 안내</t>
@@ -542,6 +530,14 @@
   </si>
   <si>
     <t>noticed_by</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_deleted</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>updated_at</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +584,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -626,11 +622,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -642,6 +649,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -946,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -955,29 +965,36 @@
     <col min="4" max="4" width="80" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -985,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -993,11 +1010,17 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1005,19 +1028,25 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1025,19 +1054,25 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1045,79 +1080,103 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6666</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1125,19 +1184,25 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6666</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1145,139 +1210,181 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6666</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6666</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6666</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1285,99 +1392,129 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="140.25" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1385,119 +1522,155 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="F22" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="153" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="F25" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="F26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="153" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="153" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1505,76 +1678,100 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="153" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="153" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="165.75" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="191.25" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="191.25" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>8</v>
+        <v>89</v>
+      </c>
+      <c r="F31" s="2">
+        <v>3333</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
